--- a/AAII_Financials/Quarterly/SUM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SUM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>SUM</t>
   </si>
@@ -656,411 +656,423 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44562</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44198</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>660100</v>
+      </c>
+      <c r="E8" s="3">
         <v>794800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>729200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>435400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>552300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>752700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>686600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>420900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>596700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>717200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>667900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>427800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>624600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>709600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>631000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>367200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>556500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>732100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>600900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>332600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>491000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>694700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>600900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>314400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>490000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>634200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>524100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>284300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>423000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>529400</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>472800</v>
+      </c>
+      <c r="E9" s="3">
         <v>543200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>492400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>354000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>390700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>534900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>484200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>353400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>435100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>486900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>467700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>346700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>418700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>501600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>439500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>286200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>370900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>483000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>405500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>267000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>345200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>471800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>410900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>247900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>318800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>409500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>335900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>217600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>273800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>335900</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>187300</v>
+      </c>
+      <c r="E10" s="3">
         <v>251600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>236800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>81400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>161600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>217800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>202400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>67500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>161600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>230300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>200200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>81100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>205900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>208000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>191500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>81000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>185600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>249100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>195400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>65600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>145800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>222900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>190000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>66500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>171200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>224700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>188200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>66700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>149200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>193500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1093,8 +1105,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1185,8 +1198,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1277,55 +1293,58 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E14" s="3">
         <v>17400</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-4100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-156100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-14200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-15700</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>4500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
-      </c>
-      <c r="R14" s="3">
-        <v>800</v>
       </c>
       <c r="S14" s="3">
         <v>800</v>
@@ -1334,135 +1353,141 @@
         <v>800</v>
       </c>
       <c r="U14" s="3">
+        <v>800</v>
+      </c>
+      <c r="V14" s="3">
         <v>400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>14900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5900</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>2600</v>
       </c>
       <c r="AC14" s="3">
         <v>2600</v>
       </c>
       <c r="AD14" s="3">
-        <v>1500</v>
+        <v>2600</v>
       </c>
       <c r="AE14" s="3">
         <v>1500</v>
       </c>
       <c r="AF14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG14" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E15" s="3">
         <v>57500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>54800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>50900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>50000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>52100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>47200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>51200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>55700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>59100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>58200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>56300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>57600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>58100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>53900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>51800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>53000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>55100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>53600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>55400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>54200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>54000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>49700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>47000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>45800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>49000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>45000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>39700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>40100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1492,192 +1517,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>576700</v>
+      </c>
+      <c r="E17" s="3">
         <v>666800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>599500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>451400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>491000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>621600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>419300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>441000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>534800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>598400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>572200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>437200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>558400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>613100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>530900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>408900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>496600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>601200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>520500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>404900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>462500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>574400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>523800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>365900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>437300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>520300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>441600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>317300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>373700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>441200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E18" s="3">
         <v>128000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>129700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>61300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>131100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>267300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-20100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>61900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>118800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>95700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>66200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>96500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>100100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-41700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>59900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>130900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>80400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-72300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>28500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>120300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>77100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-51500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>52700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>113900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>82500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-33000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>49300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>88200</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1710,468 +1742,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E20" s="3">
         <v>156700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>13100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-12600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>26300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>221100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-499100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-15500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E21" s="3">
         <v>342700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>191800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>43700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>118400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>187100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>320000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>35400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>132400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>179400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>159700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>54600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>140300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>150200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>157100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>103200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>188800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>138000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-12400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>110700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>177900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>131000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>326200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-335300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>128900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>76300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>129500</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E22" s="3">
         <v>28000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>24200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>24200</v>
       </c>
       <c r="N22" s="3">
         <v>24200</v>
       </c>
       <c r="O22" s="3">
+        <v>24200</v>
+      </c>
+      <c r="P22" s="3">
         <v>25500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>24600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>25600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>27800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>28100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>28900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>29400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>30100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>29900</v>
-      </c>
-      <c r="X22" s="3">
-        <v>28900</v>
       </c>
       <c r="Y22" s="3">
         <v>28900</v>
       </c>
       <c r="Z22" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AA22" s="3">
         <v>28800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>28700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>28900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>26000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>25100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E23" s="3">
         <v>256600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>107200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-37700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>41800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>112500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>246700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-39500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>55300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>95900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>76200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>49500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>73200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>76100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-69600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>19200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>103800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>54700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-99500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>94800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>49100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-72700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>245100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-414000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>55500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-57300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>62400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E24" s="3">
         <v>23900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>22500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-6500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>24800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>53900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>18400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-5400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>17200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-22900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-17200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>45600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>16700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-28000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>25900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>20800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-16700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>415300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-498300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2262,192 +2310,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E26" s="3">
         <v>232700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>84700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>30300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>87700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>192800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>44400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>75400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>57800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-23200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>36300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>92800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>58900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-46700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>36400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>58200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>38000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-71500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>74000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>36900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-55900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-170200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>84300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>52100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-55100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>61100</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>230000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>83600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-30800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>86500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>190100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-34300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>43800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>74200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>56700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-22500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>35200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>90700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>57100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-45000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>35700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>55800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>36400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-68800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>71300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>35500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-53700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-171700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>81300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>50000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-52400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2538,8 +2595,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2582,8 +2642,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2600,11 +2660,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>-17600</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2612,11 +2672,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>216900</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2624,14 +2684,17 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2722,8 +2785,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2814,192 +2880,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-156700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-13100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>12600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-26300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-221100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>499100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>15500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>230000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>83600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-30800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>86500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>190100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-34300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>43800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>74200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>56700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-22500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>35200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>90700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>57100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-45000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>55800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>36400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-68800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-19200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>71300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>35500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-53700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>45200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>81300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>50000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-52400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3090,197 +3165,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>230000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>83600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-30800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>86500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>190100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-34300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>43800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>74200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>56700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-22500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>35200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>90700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>57100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-45000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>55800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>36400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-68800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-19200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>71300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>35500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-53700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>45200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>81300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>50000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-52400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44562</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44198</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3313,8 +3397,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3347,100 +3432,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>374200</v>
+      </c>
+      <c r="E41" s="3">
         <v>197500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>230000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>379500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>520500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>471700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>465300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>287400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>381000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>258100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>469100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>359700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>418200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>288800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>253400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>199100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>311300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>182600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>67700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>64800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>128500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>64900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>50400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>178300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>383600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>287100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>353100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>156100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>143400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3531,376 +3620,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>297500</v>
+      </c>
+      <c r="E43" s="3">
         <v>416900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>405800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>251000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>263200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>397500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>365100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>252600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>294800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>367500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>345300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>267200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>263400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>353400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>324500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>242500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>266300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>386800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>340000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>212500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>233100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>301700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>268800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>180100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>198300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>295500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>247500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>154800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>162400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>247200</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>241400</v>
+      </c>
+      <c r="E44" s="3">
         <v>243100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>246300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>234600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>212500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>202800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>209900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>187000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>180800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>195300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>198200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>210900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>200300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>209800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>231900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>231400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>204800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>197000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>208100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>214000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>213900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>277400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>289700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>239400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>194000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>221100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>212100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>201900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>165100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>203900</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>819100</v>
+      </c>
+      <c r="E45" s="3">
         <v>19700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>50900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>20600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>19200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>16100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>15700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>13700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>11700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>12000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>12800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1732100</v>
+      </c>
+      <c r="E46" s="3">
         <v>877200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>906300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>890900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1018400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1093300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1056500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>777800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>869600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>834800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1027900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>858400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>893300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>865500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>822000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>688300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>796300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>778400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>628400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>510600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>591500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>659700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>621300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>611600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>783600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>815300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>825100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>524900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>483700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>491100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3991,192 +4095,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2013400</v>
+      </c>
+      <c r="E48" s="3">
         <v>2012900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2016000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1904100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1851600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1799500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1817300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1795400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1873100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1868500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1894000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1925900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1878700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1791600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1782600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1799200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1780200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1795400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1822800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1834300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1780100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1751800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1733700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1672900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1615400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1620100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1555800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1528300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1446500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1456500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1292900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1310300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1298200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1230000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1203900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1199000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1212700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1213300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1233100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1245200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1247800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1272900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1249100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1341000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1235600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1218400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1223200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1222900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1215800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1213300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1210500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1166500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1131300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1126100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1053200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1029800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>935900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>865700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>800200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>785700</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4267,8 +4380,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4359,100 +4475,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>111100</v>
+      </c>
+      <c r="E52" s="3">
         <v>164600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>175000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>190000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>181800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>193200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>204400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>356800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>263300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>268200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>282700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>294000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>286900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>294000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>271000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>286400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>267900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>245400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>287900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>303100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>275500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>318400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>338000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>346100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>335200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>527600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>48400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>53000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>51100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>47800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4543,100 +4665,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5149600</v>
+      </c>
+      <c r="E54" s="3">
         <v>4365000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4395500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4214900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4255700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4285000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4290800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4143200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4239100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4216600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4452400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4351300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4308000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4292200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4111200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3992300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4067600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4042100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3954900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3861400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3857600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3896300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3824300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3756600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3787300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3992800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3365200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2971900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2781500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2781000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4669,8 +4797,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4703,560 +4832,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E57" s="3">
         <v>173100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>171200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>139000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>104000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>166600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>167600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>146300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>128200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>155900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>152300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>150200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>120800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>149500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>138300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>122400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>116400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>152200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>131400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>101800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>107700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>140200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>144300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>110300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>98700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>134900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>116800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>105400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>81600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>113300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E58" s="3">
         <v>7200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>24000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>23800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>25700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>27600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>31000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>32800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>31200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>28700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>23900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>23600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>22600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>22200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>21900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>19700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>23800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>29100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>24000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>27000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>26300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>23900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>18300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>191500</v>
+      </c>
+      <c r="E59" s="3">
         <v>168500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>167200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>112200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>139800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>140100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>148000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>138200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>156900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>151200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>163900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>143800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>170900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>173600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>167200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>134800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>159000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>156200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>150900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>135200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>131000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>126500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>131400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>141800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>127200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>153200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>134000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>114000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>139500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>134700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>323000</v>
+      </c>
+      <c r="E60" s="3">
         <v>348900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>347000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>260500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>255800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>322800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>333000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>305100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>309100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>330900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>341900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>321700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>322700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>355900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>336700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>285800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>299300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>332100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>304800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>259300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>260700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>286400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>299500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>281300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>250000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>315100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>277200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>243300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>239300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>267300</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2298000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1493200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1493100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1494100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1495700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1606000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1728300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2031700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2035900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1924100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1893200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1849500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1850300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1851100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1853400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1854200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1855300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1807500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1808200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1807300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1808500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1810800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1807100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1807700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1513100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1514500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1515400</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E62" s="3">
         <v>215100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>481400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>480400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>492100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1982700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2007900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2081100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>500800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>385700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>383900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>379100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>445000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>473600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>463100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>460300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>472400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>469900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>473100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>468300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>447300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>442900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>439700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>431400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>454800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>653200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>167300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>167800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>167700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5347,8 +5495,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5439,8 +5590,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5531,100 +5685,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2842500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2071400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2334900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2247200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2256400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2326300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2361800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2406000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2425600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2454800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2768000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2749700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2710200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2740900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2665500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2610700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2640100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2670700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2645300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2594500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2529900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2551500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2557800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2531600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2528800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2791200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2265600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1937200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1939400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2006400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5657,8 +5817,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5749,8 +5910,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5841,8 +6005,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5933,8 +6100,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6025,100 +6195,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>876800</v>
+      </c>
+      <c r="E72" s="3">
         <v>873800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>643700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>560100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>590900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>620300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>587300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>397200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>479000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>435100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>360900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>304300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>326800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>291600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>200900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>143800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>188800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>153100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>97400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>61000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>129700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>148900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>77600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>42100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>95800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>95600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>16600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-33400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6209,8 +6385,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6301,8 +6480,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6393,100 +6575,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2307000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2293600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2060600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1967700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1999300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1958600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1929000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1737300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1813600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1761900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1684400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1601500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1597800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1551200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1445700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1381600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1427400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1371400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1309500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1266900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1327700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1344900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1266400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1224900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1258500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1201600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1099500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1034600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>842000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>774600</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6577,197 +6765,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44562</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44198</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>230000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>83600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-30800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>86500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>190100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-34300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>43800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>74200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>56700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-22500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>35200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>90700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>57100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-45000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>55800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>36400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-68800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-19200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>71300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>35500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-53700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>45200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>81300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>50000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-52400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6800,100 +6997,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E83" s="3">
         <v>58100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>56700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>53900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>52300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>52700</v>
       </c>
       <c r="I83" s="3">
         <v>52700</v>
       </c>
       <c r="J83" s="3">
+        <v>52700</v>
+      </c>
+      <c r="K83" s="3">
         <v>54800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>57400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>59400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>59300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>59100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>65300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>52400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>55400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>54700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>55900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>56000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>53900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>57000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>55900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>54300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>53000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>45600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>52500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>49900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>47400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>43300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>42600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6984,8 +7185,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7076,8 +7280,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7168,8 +7375,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7260,8 +7470,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7352,100 +7565,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>195200</v>
+      </c>
+      <c r="E89" s="3">
         <v>149600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>93700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>151900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>115900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>33000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-16700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>154600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>132700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>96000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>190800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>156300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>100600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-38900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>173300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>147900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>46600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-30700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>138800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>104300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>17600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-51400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>159800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>121300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>56700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-45500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>160300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7478,100 +7697,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-73400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-55300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-63300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-59400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-71800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-57800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-41900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-37300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-63000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-69800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-37200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-34300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-43900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-61800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-37700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-34200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-43400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-62200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-36900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-52100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-82200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-46700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-51100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-31500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7662,8 +7885,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7754,100 +7980,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-54900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-242300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-118300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-93100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>223900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-35800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-34500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-32600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-155500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-40600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-56900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-33000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-28900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-38400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-62400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-67700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-81900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-115800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-154200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-47000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-191800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-155600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-158100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-35000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-58300</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7880,8 +8112,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7972,8 +8205,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8064,8 +8300,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8156,8 +8395,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8248,280 +8490,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>785000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-126600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-23100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-82700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-78300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-67700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-307600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>8300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-29300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>34300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-15600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-11700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>29200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-7200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-29600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-16300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>295800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>216200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-13400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-30100</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-400</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>500</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>100</v>
       </c>
       <c r="AD101" s="3">
         <v>100</v>
       </c>
       <c r="AE101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>976700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-32500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-149400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-141000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>48800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>177900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-93600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>122900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-211000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>109400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-58400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>129400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>35400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>54300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-112200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>128700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>114900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-63700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>63600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-127900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-205300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>96500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-66000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>197000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>111700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>22500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SUM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SUM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>SUM</t>
   </si>
@@ -656,423 +656,436 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44562</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44198</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43099</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>805000</v>
+      </c>
+      <c r="E8" s="3">
         <v>660100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>794800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>729200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>435400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>552300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>752700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>686600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>420900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>596700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>717200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>667900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>427800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>624600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>709600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>631000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>367200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>556500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>732100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>600900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>332600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>491000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>694700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>600900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>314400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>490000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>634200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>524100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>284300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>423000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>529400</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>624000</v>
+      </c>
+      <c r="E9" s="3">
         <v>472800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>543200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>492400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>354000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>390700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>534900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>484200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>353400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>435100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>486900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>467700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>346700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>418700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>501600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>439500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>286200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>370900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>483000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>405500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>267000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>345200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>471800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>410900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>247900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>318800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>409500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>335900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>217600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>273800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>335900</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E10" s="3">
         <v>187300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>251600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>236800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>81400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>161600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>217800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>202400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>67500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>161600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>230300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>200200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>81100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>205900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>208000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>191500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>81000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>185600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>249100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>195400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>65600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>145800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>222900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>190000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>66500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>171200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>224700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>188200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>66700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>149200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>193500</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1106,8 +1119,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1201,8 +1215,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1296,58 +1313,61 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-7700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>17400</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-156100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-14200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-4700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-15700</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>4500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
-      </c>
-      <c r="S14" s="3">
-        <v>800</v>
       </c>
       <c r="T14" s="3">
         <v>800</v>
@@ -1356,138 +1376,144 @@
         <v>800</v>
       </c>
       <c r="V14" s="3">
+        <v>800</v>
+      </c>
+      <c r="W14" s="3">
         <v>400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>14900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5900</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>2600</v>
       </c>
       <c r="AD14" s="3">
         <v>2600</v>
       </c>
       <c r="AE14" s="3">
-        <v>1500</v>
+        <v>2600</v>
       </c>
       <c r="AF14" s="3">
         <v>1500</v>
       </c>
       <c r="AG14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AH14" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E15" s="3">
         <v>54400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>57500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>54800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>50900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>50000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>52100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>47200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>51200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>55700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>59100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>58200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>56300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>57600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>58100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>53900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>51800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>53000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>55100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>53600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>55400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>54200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>54000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>49700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>47000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>45800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>49000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>45000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>39700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>40100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1518,198 +1544,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>840300</v>
+      </c>
+      <c r="E17" s="3">
         <v>576700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>666800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>599500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>451400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>491000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>621600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>419300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>441000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>534800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>598400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>572200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>437200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>558400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>613100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>530900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>408900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>496600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>601200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>520500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>404900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>462500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>574400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>523800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>365900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>437300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>520300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>441600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>317300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>373700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>441200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-35300</v>
+      </c>
+      <c r="E18" s="3">
         <v>83400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>128000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>129700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>61300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>131100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>267300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-20100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>61900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>118800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>95700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>66200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>96500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>100100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-41700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>59900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>130900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>80400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-72300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>28500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>120300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>77100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-51500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>52700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>113900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>82500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-33000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>49300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>88200</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1743,483 +1776,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E20" s="3">
         <v>15700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>156700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>13100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-12600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>26300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>221100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-499100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-15500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E21" s="3">
         <v>157000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>342700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>191800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>43700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>118400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>187100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>320000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>35400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>132400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>179400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>159700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>54600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>140300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>150200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>157100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>103200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>188800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>138000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-12400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>110700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>177900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>131000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>326200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-335300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>128900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>11000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>76300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>129500</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E22" s="3">
         <v>30800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>22000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>19700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>24200</v>
       </c>
       <c r="O22" s="3">
         <v>24200</v>
       </c>
       <c r="P22" s="3">
+        <v>24200</v>
+      </c>
+      <c r="Q22" s="3">
         <v>25500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>24600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>25600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>27800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>28100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>28900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>29400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>30100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>29900</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>28900</v>
       </c>
       <c r="Z22" s="3">
         <v>28900</v>
       </c>
       <c r="AA22" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AB22" s="3">
         <v>28800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>28700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>28900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>26000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>25000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>25100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-78300</v>
+      </c>
+      <c r="E23" s="3">
         <v>68300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>256600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>107200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-37700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>41800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>112500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>246700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-39500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>55300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>95900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>76200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>49500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>73200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>76100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-69600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>19200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>103800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>54700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-99500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>24900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>94800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>49100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-72700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>245100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-414000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>55500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-57300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>62400</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E24" s="3">
         <v>64900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>23900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>22500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-6500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>24800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>53900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-19600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>17200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-22900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-17200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>45600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>16700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-28000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>25900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>20800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-16700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>415300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-498300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2313,198 +2362,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="E26" s="3">
         <v>3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>232700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>84700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>30300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>87700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>192800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-34800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>44400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>75400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>57800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-23200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>36300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>92800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>58900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-46700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>36400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>58200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>38000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-71500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>74000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>36900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-55900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-170200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>84300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>52100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-55100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>61100</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="E27" s="3">
         <v>3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>230000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>83600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-30800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>29800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>86500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>190100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-34300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>43800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>74200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>56700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-22500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>35200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>90700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>57100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-45000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>55800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>36400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-68800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>71300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>35500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-53700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-171700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>81300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>50000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-52400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2598,8 +2656,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2645,8 +2706,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2663,11 +2724,11 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-17600</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2675,11 +2736,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>216900</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2687,14 +2748,17 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2788,8 +2852,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2883,198 +2950,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-15700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-156700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-13100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>12600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-26300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-221100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>499100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>15500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="E33" s="3">
         <v>3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>230000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>83600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-30800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>29800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>86500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>190100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-34300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>43800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>74200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>56700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-22500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>90700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>57100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-45000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>55800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>36400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-68800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-19200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>71300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>35500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-53700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>45200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>81300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>50000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-52400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3168,203 +3244,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="E35" s="3">
         <v>3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>230000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>83600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-30800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>29800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>86500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>190100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-34300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>43800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>74200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>56700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-22500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>90700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>57100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-45000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>55800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>36400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-68800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-19200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>71300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>35500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-53700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>45200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>81300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>50000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-52400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44562</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44198</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43099</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3398,8 +3483,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3433,103 +3519,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>498100</v>
+      </c>
+      <c r="E41" s="3">
         <v>374200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>197500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>230000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>379500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>520500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>471700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>465300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>287400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>381000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>258100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>469100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>359700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>418200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>288800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>253400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>199100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>311300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>182600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>67700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>64800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>128500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>64900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>50400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>178300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>383600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>287100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>353100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>156100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>143400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3623,388 +3713,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>466300</v>
+      </c>
+      <c r="E43" s="3">
         <v>297500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>416900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>405800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>251000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>263200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>397500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>365100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>252600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>294800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>367500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>345300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>267200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>263400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>353400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>324500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>242500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>266300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>386800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>340000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>212500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>233100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>301700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>268800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>180100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>198300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>295500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>247500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>154800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>162400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>247200</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>338500</v>
+      </c>
+      <c r="E44" s="3">
         <v>241400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>243100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>246300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>234600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>212500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>202800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>209900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>187000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>180800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>195300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>198200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>210900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>200300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>209800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>231900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>231400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>204800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>197000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>208100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>214000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>213900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>277400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>289700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>239400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>194000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>221100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>212100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>201900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>165100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>203900</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E45" s="3">
         <v>819100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>19700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>50900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>20600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>19200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>16100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>15700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>12400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>13700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>11700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>12400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>12000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>12800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1345000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1732100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>877200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>906300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>890900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1018400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1093300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1056500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>777800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>869600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>834800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1027900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>858400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>893300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>865500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>822000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>688300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>796300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>778400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>628400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>510600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>591500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>659700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>621300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>611600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>783600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>815300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>825100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>524900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>483700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>491100</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4098,198 +4203,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4525600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2013400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2012900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2016000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1904100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1851600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1799500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1817300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1795400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1873100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1868500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1894000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1925900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1878700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1791600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1782600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1799200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1780200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1795400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1822800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1834300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1780100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1751800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1733700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1672900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1615400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1620100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1555800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1528300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1446500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1456500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2170100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1292900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1310300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1298200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1230000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1203900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1199000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1212700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1213300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1233100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1245200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1247800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1272900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1249100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1341000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1235600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1218400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1223200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1222900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1215800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1213300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1210500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1166500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1131300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1126100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1053200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1029800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>935900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>865700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>800200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>785700</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4383,8 +4497,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4478,103 +4595,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>89300</v>
+      </c>
+      <c r="E52" s="3">
         <v>111100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>164600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>175000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>190000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>181800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>193200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>204400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>356800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>263300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>268200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>282700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>294000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>286900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>294000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>271000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>286400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>267900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>245400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>287900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>303100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>275500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>318400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>338000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>346100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>335200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>527600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>48400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>53000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>51100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>47800</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4668,103 +4791,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8129900</v>
+      </c>
+      <c r="E54" s="3">
         <v>5149600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4365000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4395500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4214900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4255700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4285000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4290800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4143200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4239100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4216600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4452400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4351300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4308000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4292200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4111200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3992300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4067600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4042100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3954900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3861400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3857600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3896300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3824300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3756600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3787300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3992800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3365200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2971900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2781500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2781000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4798,8 +4927,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4833,578 +4963,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>290900</v>
+      </c>
+      <c r="E57" s="3">
         <v>123600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>173100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>171200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>139000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>104000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>166600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>167600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>146300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>128200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>155900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>152300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>150200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>120800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>149500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>138300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>122400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>116400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>152200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>131400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>101800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>107700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>140200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>144300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>110300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>98700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>134900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>116800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>105400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>81600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>113300</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E58" s="3">
         <v>7800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>23800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>25700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>27600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>31000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>32800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>31200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>28700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>23900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>23600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>22600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>22200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>21900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>19700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>23800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>29100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>24000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>27000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>26300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>23900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>18300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>218800</v>
+      </c>
+      <c r="E59" s="3">
         <v>191500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>168500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>167200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>112200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>139800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>140100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>148000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>138200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>156900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>151200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>163900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>143800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>170900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>173600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>167200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>134800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>159000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>156200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>150900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>135200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>131000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>126500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>131400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>141800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>127200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>153200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>134000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>114000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>139500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>134700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>522000</v>
+      </c>
+      <c r="E60" s="3">
         <v>323000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>348900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>347000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>260500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>255800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>322800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>333000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>305100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>309100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>330900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>341900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>321700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>322700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>355900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>336700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>285800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>299300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>332100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>304800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>259300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>260700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>286400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>299500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>281300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>250000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>315100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>277200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>243300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>239300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>267300</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2804900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2298000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1493200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1493100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1494100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1495700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1606000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1728300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2031700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2035900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1924100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1893200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1849500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1850300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1851100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1853400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1854200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1855300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1807500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1808200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1807300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1808500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1810800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1807100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1807700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1513100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1514500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1515400</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>584400</v>
+      </c>
+      <c r="E62" s="3">
         <v>212000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>215100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>481400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>480400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>492100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1982700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2007900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2081100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>500800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>385700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>383900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>379100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>445000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>473600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>463100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>460300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>472400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>469900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>473100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>468300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>447300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>442900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>439700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>431400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>454800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>653200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>167300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>167800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>167700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5498,8 +5647,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5593,8 +5745,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5688,103 +5843,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3911300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2842500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2071400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2334900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2247200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2256400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2326300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2361800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2406000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2425600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2454800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2768000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2749700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2710200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2740900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2665500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2610700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2640100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2670700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2645300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2594500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2529900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2551500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2557800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2531600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2528800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2791200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2265600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1937200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1939400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2006400</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5818,8 +5979,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5913,8 +6075,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6008,8 +6173,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6103,8 +6271,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6198,103 +6369,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>809900</v>
+      </c>
+      <c r="E72" s="3">
         <v>876800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>873800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>643700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>560100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>590900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>620300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>587300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>397200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>479000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>435100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>360900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>304300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>326800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>291600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>200900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>143800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>188800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>153100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>97400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>61000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>129700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>148900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>77600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>42100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>95800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>95600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>16600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-33400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6388,8 +6565,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6483,8 +6663,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6578,103 +6761,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4218600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2307000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2293600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2060600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1967700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1999300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1958600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1929000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1737300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1813600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1761900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1684400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1601500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1597800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1551200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1445700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1381600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1427400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1371400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1309500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1266900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1327700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1344900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1266400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1224900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1258500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1201600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1099500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1034600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>842000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>774600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6768,203 +6957,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44562</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44198</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43099</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="E81" s="3">
         <v>3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>230000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>83600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-30800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>29800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>86500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>190100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-34300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>43800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>74200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>56700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-22500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>90700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>57100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-45000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>55800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>36400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-68800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-19200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>71300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>35500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-53700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>45200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>81300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>50000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-52400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6998,103 +7196,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>106400</v>
+      </c>
+      <c r="E83" s="3">
         <v>57900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>58100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>56700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>53900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>52300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>52700</v>
       </c>
       <c r="J83" s="3">
         <v>52700</v>
       </c>
       <c r="K83" s="3">
+        <v>52700</v>
+      </c>
+      <c r="L83" s="3">
         <v>54800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>57400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>59400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>59300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>59100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>65300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>52400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>55400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>54700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>55900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>56000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>53900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>57000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>55900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>54300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>53000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>45600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>52500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>49900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>47400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>43300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>42600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7188,8 +7390,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7283,8 +7488,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7378,8 +7586,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7473,8 +7684,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7568,103 +7782,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E89" s="3">
         <v>195200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>149600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>93700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>151900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>115900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>33000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-16700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>154600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>132700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>96000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>190800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>156300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>100600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-38900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>173300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>147900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>46600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-30700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>138800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>104300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>17600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-51400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>159800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>121300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>56700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-45500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>160300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7698,103 +7918,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-79900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-73400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-55300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-63600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-77700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-59400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-71800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-57800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-41900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-37300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-63000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-69800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-34300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-43900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-61800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-37700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-34200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-43400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-62200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-36900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-52100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-82200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-46700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-51100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-31500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7888,8 +8112,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7983,103 +8210,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1103400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-54900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-242300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-118300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-93100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>223900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>4900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-34500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-155500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-40600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-56900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-33000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-28900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-38400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-62400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-67700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-81900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-115800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-154200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-47000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-191800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-155600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-158100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-35000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-58300</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8113,8 +8346,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8208,8 +8442,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8303,8 +8540,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8398,8 +8638,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8493,289 +8736,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>468700</v>
+      </c>
+      <c r="E100" s="3">
         <v>785000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-126600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-23100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-82700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-78300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-67700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-307600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>8300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-29300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>34300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-15600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-11700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>29200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-29600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>295800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>216200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-13400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-30100</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-300</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-400</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>500</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>100</v>
       </c>
       <c r="AE101" s="3">
         <v>100</v>
       </c>
       <c r="AF101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-676100</v>
+      </c>
+      <c r="E102" s="3">
         <v>976700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-32500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-149400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-141000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>48800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>177900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-93600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>122900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-211000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>109400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-58400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>129400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>35400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>54300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-112200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>128700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>114900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-63700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>63600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-127900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-205300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>96500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-66000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>197000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>12700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>111700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>22500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SUM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SUM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>SUM</t>
   </si>
@@ -656,436 +656,449 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44562</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44198</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1118300</v>
+      </c>
+      <c r="E8" s="3">
         <v>805000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>660100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>794800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>729200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>435400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>552300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>752700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>686600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>420900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>596700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>717200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>667900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>427800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>624600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>709600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>631000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>367200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>556500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>732100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>600900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>332600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>491000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>694700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>600900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>314400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>490000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>634200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>524100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>284300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>423000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>529400</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>750000</v>
+      </c>
+      <c r="E9" s="3">
         <v>624000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>472800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>543200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>492400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>354000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>390700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>534900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>484200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>353400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>435100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>486900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>467700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>346700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>418700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>501600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>439500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>286200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>370900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>483000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>405500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>267000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>345200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>471800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>410900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>247900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>318800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>409500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>335900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>217600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>273800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>335900</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>368300</v>
+      </c>
+      <c r="E10" s="3">
         <v>181000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>187300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>251600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>236800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>81400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>161600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>217800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>202400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>67500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>161600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>230300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>200200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>81100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>205900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>208000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>191500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>81000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>185600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>249100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>195400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>65600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>145800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>222900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>190000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>66500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>171200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>224700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>188200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>66700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>149200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>193500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1120,8 +1133,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1218,8 +1232,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1316,61 +1333,64 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E14" s="3">
         <v>52700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-7700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>17400</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-156100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-14200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>4500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
-      </c>
-      <c r="T14" s="3">
-        <v>800</v>
       </c>
       <c r="U14" s="3">
         <v>800</v>
@@ -1379,141 +1399,147 @@
         <v>800</v>
       </c>
       <c r="W14" s="3">
+        <v>800</v>
+      </c>
+      <c r="X14" s="3">
         <v>400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>14900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5900</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>2600</v>
       </c>
       <c r="AE14" s="3">
         <v>2600</v>
       </c>
       <c r="AF14" s="3">
-        <v>1500</v>
+        <v>2600</v>
       </c>
       <c r="AG14" s="3">
         <v>1500</v>
       </c>
       <c r="AH14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AI14" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>104400</v>
+      </c>
+      <c r="E15" s="3">
         <v>96000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>54400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>57500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>54800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>50900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>50000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>52100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>47200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>51200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>55700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>59100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>58200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>56300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>57600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>58100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>53900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>51800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>53000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>55100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>53600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>55400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>54200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>54000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>49700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>47000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>45800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>49000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>45000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>39700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>40100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1545,204 +1571,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>941600</v>
+      </c>
+      <c r="E17" s="3">
         <v>840300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>576700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>666800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>599500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>451400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>491000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>621600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>419300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>441000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>534800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>598400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>572200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>437200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>558400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>613100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>530900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>408900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>496600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>601200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>520500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>404900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>462500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>574400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>523800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>365900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>437300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>520300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>441600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>317300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>373700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>441200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>176700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-35300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>83400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>128000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>129700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>61300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>131100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>267300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-20100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>61900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>118800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>95700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>66200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>96500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>100100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-41700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>59900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>130900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>80400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-72300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>28500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>120300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>77100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-51500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>52700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>113900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>82500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-33000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>49300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>88200</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1777,498 +1810,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E20" s="3">
         <v>8900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>15700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>156700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>13100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>26300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>7700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>221100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-499100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-15500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>285100</v>
+      </c>
+      <c r="E21" s="3">
         <v>79900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>157000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>342700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>191800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>43700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>118400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>187100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>320000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>35400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>132400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>179400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>159700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>54600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>140300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>150200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>157100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>103200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>188800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>138000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>110700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>177900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>131000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>326200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-335300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>128900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>11000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>76300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>129500</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E22" s="3">
         <v>51900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>28000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>19700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24100</v>
-      </c>
-      <c r="O22" s="3">
-        <v>24200</v>
       </c>
       <c r="P22" s="3">
         <v>24200</v>
       </c>
       <c r="Q22" s="3">
+        <v>24200</v>
+      </c>
+      <c r="R22" s="3">
         <v>25500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>24600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>25600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>27800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>28100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>28900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>29400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>30100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>29900</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>28900</v>
       </c>
       <c r="AA22" s="3">
         <v>28900</v>
       </c>
       <c r="AB22" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AC22" s="3">
         <v>28800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>28700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>28900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>26000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>25000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>25100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>131900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-78300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>68300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>256600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>107200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-37700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>41800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>112500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>246700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-39500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>55300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>95900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>76200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-28700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>49500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>73200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>76100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-69600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>19200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>103800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>54700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-99500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>94800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>49100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-72700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>245100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-414000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>55500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-57300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>62400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-11100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>64900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>23900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>22500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-6500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>24800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>53900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>20500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>18400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>13100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-19600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>17200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-22900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-17200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>45600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>16700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>25900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>20800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>12200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-16700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>415300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-498300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2365,204 +2414,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-67300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>232700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>84700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>30300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>87700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>192800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>44400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>75400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>57800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>36300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>92800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>58900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-46700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>36400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>58200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>38000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-71500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>74000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>36900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-55900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-170200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>84300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>52100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-55100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>61100</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-66900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>230000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>83600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-30800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>29800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>86500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>190100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>43800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>74200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>56700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-22500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>35200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>90700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>57100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-45000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>35700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>55800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>36400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-68800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>71300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>35500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-53700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-171700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>81300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>50000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-52400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2659,8 +2717,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2709,8 +2770,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2727,11 +2788,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-17600</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2739,11 +2800,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>216900</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2751,14 +2812,17 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2855,8 +2919,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2953,204 +3020,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-15700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-156700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-13100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-26300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-221100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>499100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>15500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-66900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>230000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>83600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-30800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>29800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>86500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>190100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>43800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>74200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>56700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-22500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>35200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>90700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>57100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-45000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>55800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>36400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-68800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-19200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>71300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>35500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-53700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>45200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>81300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>50000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-52400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3247,209 +3323,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-66900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>230000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>83600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-30800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>29800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>86500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>190100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>43800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>74200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>56700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-22500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>35200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>90700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>57100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-45000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>55800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>36400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-68800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-19200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>71300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>35500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-53700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>45200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>81300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>50000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-52400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44562</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44198</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3484,8 +3569,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3520,106 +3606,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>538700</v>
+      </c>
+      <c r="E41" s="3">
         <v>498100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>374200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>197500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>230000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>379500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>520500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>471700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>465300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>287400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>381000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>258100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>469100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>359700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>418200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>288800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>253400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>199100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>311300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>182600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>67700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>64800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>128500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>64900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>50400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>178300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>383600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>287100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>353100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>156100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>143400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3716,400 +3806,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>584000</v>
+      </c>
+      <c r="E43" s="3">
         <v>466300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>297500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>416900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>405800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>251000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>263200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>397500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>365100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>252600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>294800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>367500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>345300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>267200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>263400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>353400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>324500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>242500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>266300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>386800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>340000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>212500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>233100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>301700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>268800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>180100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>198300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>295500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>247500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>154800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>162400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>247200</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>349100</v>
+      </c>
+      <c r="E44" s="3">
         <v>338500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>241400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>243100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>246300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>234600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>212500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>202800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>209900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>187000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>180800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>195300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>198200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>210900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>200300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>209800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>231900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>231400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>204800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>197000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>208100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>214000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>213900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>277400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>289700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>239400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>194000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>221100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>212100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>201900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>165100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>203900</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E45" s="3">
         <v>42000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>819100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>19700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>24200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>50900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>20600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>19200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>16100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>15700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>12400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>13700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>11700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>12400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>12000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>12800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1500800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1345000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1732100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>877200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>906300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>890900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1018400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1093300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1056500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>777800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>869600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>834800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1027900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>858400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>893300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>865500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>822000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>688300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>796300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>778400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>628400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>510600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>591500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>659700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>621300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>611600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>783600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>815300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>825100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>524900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>483700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>491100</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4206,204 +4311,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4443400</v>
+      </c>
+      <c r="E48" s="3">
         <v>4525600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2013400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2012900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2016000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1904100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1851600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1799500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1817300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1795400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1873100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1868500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1894000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1925900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1878700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1791600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1782600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1799200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1780200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1795400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1822800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1834300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1780100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1751800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1733700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1672900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1615400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1620100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1555800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1528300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1446500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1456500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2261300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2170100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1292900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1310300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1298200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1230000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1203900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1199000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1212700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1213300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1233100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1245200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1247800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1272900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1249100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1341000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1235600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1218400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1223200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1222900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1215800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1213300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1210500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1166500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1131300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1126100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1053200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1029800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>935900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>865700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>800200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>785700</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4500,8 +4614,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4598,106 +4715,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E52" s="3">
         <v>89300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>111100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>164600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>175000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>190000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>181800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>193200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>204400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>356800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>263300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>268200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>282700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>294000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>286900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>294000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>271000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>286400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>267900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>245400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>287900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>303100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>275500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>318400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>338000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>346100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>335200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>527600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>48400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>53000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>51100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>47800</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4794,106 +4917,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8314000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8129900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5149600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4365000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4395500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4214900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4255700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4285000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4290800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4143200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4239100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4216600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4452400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4351300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4308000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4292200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4111200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3992300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4067600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4042100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3954900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3861400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3857600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3896300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3824300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3756600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3787300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3992800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3365200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2971900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2781500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2781000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4928,8 +5057,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4964,596 +5094,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>282100</v>
+      </c>
+      <c r="E57" s="3">
         <v>290900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>123600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>173100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>171200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>139000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>104000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>166600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>167600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>146300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>128200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>155900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>152300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>150200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>120800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>149500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>138300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>122400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>116400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>152200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>131400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>101800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>107700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>140200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>144300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>110300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>98700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>134900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>116800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>105400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>81600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>113300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E58" s="3">
         <v>12300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>23800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>25700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>27600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>31000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>32800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>31200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>28700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>23900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>23600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>22600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>22200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>21900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>19700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>23800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>29100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>24000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>27000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>26300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>23900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>18300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>279100</v>
+      </c>
+      <c r="E59" s="3">
         <v>218800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>191500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>168500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>167200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>112200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>139800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>140100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>148000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>138200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>156900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>151200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>163900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>143800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>170900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>173600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>167200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>134800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>159000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>156200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>150900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>135200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>131000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>126500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>131400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>141800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>127200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>153200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>134000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>114000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>139500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>134700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>573900</v>
+      </c>
+      <c r="E60" s="3">
         <v>522000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>323000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>348900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>347000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>260500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>255800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>322800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>333000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>305100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>309100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>330900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>341900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>321700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>322700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>355900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>336700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>285800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>299300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>332100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>304800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>259300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>260700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>286400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>299500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>281300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>250000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>315100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>277200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>243300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>239300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>267300</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2804500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2804900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2298000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1493200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1493100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1494100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1495700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1606000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1728300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2031700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2035900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1924100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1893200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1849500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1850300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1851100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1853400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1854200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1855300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1807500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1808200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1807300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1808500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1810800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1807100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1807700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1513100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1514500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1515400</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>602800</v>
+      </c>
+      <c r="E62" s="3">
         <v>584400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>212000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>215100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>481400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>480400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>492100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1982700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2007900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2081100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>500800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>385700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>383900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>379100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>445000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>473600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>463100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>460300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>472400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>469900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>473100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>468300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>447300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>442900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>439700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>431400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>454800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>653200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>167300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>167800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>167700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5650,8 +5799,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5748,8 +5900,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5846,106 +6001,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3981200</v>
+      </c>
+      <c r="E66" s="3">
         <v>3911300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2842500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2071400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2334900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2247200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2256400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2326300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2361800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2406000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2425600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2454800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2768000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2749700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2710200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2740900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2665500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2610700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2640100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2670700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2645300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2594500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2529900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2551500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2557800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2531600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2528800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2791200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2265600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1937200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1939400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2006400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5980,8 +6141,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6078,8 +6240,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6176,8 +6341,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6274,8 +6442,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6372,106 +6543,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>916000</v>
+      </c>
+      <c r="E72" s="3">
         <v>809900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>876800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>873800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>643700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>560100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>590900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>620300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>587300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>397200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>479000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>435100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>360900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>304300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>326800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>291600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>200900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>143800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>188800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>153100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>97400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>61000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>129700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>148900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>77600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>42100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>95800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>95600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-33400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6568,8 +6745,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6666,8 +6846,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6764,106 +6947,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4332700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4218600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2307000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2293600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2060600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1967700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1999300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1958600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1929000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1737300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1813600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1761900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1684400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1601500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1597800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1551200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1445700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1381600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1427400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1371400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1309500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1266900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1327700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1344900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1266400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1224900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1258500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1201600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1099500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1034600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>842000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>774600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6960,209 +7149,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44562</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44198</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-66900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>230000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>83600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-30800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>29800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>86500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>190100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>43800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>74200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>56700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-22500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>35200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>90700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>57100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-45000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>55800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>36400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-68800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-19200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>71300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>35500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-53700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>45200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>81300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>50000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-52400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7197,106 +7395,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E83" s="3">
         <v>106400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>57900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>58100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>56700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>53900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>52300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>52700</v>
       </c>
       <c r="K83" s="3">
         <v>52700</v>
       </c>
       <c r="L83" s="3">
+        <v>52700</v>
+      </c>
+      <c r="M83" s="3">
         <v>54800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>57400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>59400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>59300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>59100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>65300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>52400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>55400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>54700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>55900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>56000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>53900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>57000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>55900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>54300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>53000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>45600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>52500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>49900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>47400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>43300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>42600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7393,8 +7595,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7491,8 +7696,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7589,8 +7797,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7687,8 +7898,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7785,106 +7999,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>151600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-40200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>195200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>149600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>93700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>151900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>115900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>33000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-16700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>154600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>132700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>96000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>190800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>156300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>100600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-38900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>173300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>147900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>46600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>138800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>104300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>17600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-51400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>159800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>121300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>56700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-45500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>160300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7919,106 +8139,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-117400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-79900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-73400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-63300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-63600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-77700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-59400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-71800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-57800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-41900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-37300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-63000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-69800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-37200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-34300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-43900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-61800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-37700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-34200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-43400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-62200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-36900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-52100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-82200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-46700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-51100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-31500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8115,8 +8339,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8213,106 +8440,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-109000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1103400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-54900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-242300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-118300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-93100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>223900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-25900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>4900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-32600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-155500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-40600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-56900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-33000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-28900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-38400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-62400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-67700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-81900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-115800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-154200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-47000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-191800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-155600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-158100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-35000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-58300</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8347,8 +8580,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8445,8 +8679,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8543,8 +8780,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8641,8 +8881,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8739,298 +8982,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E100" s="3">
         <v>468700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>785000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-126600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-23100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-82700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-78300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-67700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-307600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-29300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>34300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-15600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-11700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>29200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-29600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-16300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>295800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>216200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-13400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-30100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-300</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-400</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>500</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>100</v>
       </c>
       <c r="AF101" s="3">
         <v>100</v>
       </c>
       <c r="AG101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-676100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>976700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-32500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-149400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-141000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>48800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>177900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-93600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>122900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-211000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>109400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-58400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>129400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>35400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>54300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-112200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>128700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>114900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-63700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>63600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>14500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-127900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-205300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>96500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-66000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>197000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>12700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>111700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>22500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SUM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SUM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>SUM</t>
   </si>
@@ -656,449 +656,462 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44562</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44198</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43827</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43463</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43099</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1171100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1118300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>805000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>660100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>794800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>729200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>435400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>552300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>752700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>686600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>420900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>596700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>717200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>667900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>427800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>624600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>709600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>631000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>367200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>556500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>732100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>600900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>332600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>491000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>694700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>600900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>314400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>490000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>634200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>524100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>284300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>423000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>529400</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>788300</v>
+      </c>
+      <c r="E9" s="3">
         <v>750000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>624000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>472800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>543200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>492400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>354000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>390700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>534900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>484200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>353400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>435100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>486900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>467700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>346700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>418700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>501600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>439500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>286200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>370900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>483000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>405500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>267000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>345200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>471800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>410900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>247900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>318800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>409500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>335900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>217600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>273800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>335900</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>382800</v>
+      </c>
+      <c r="E10" s="3">
         <v>368300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>181000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>187300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>251600</v>
       </c>
-      <c r="H10" s="3">
-        <v>236800</v>
-      </c>
       <c r="I10" s="3">
+        <v>236700</v>
+      </c>
+      <c r="J10" s="3">
         <v>81400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>161600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>217800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>202400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>67500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>161600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>230300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>200200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>81100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>205900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>208000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>191500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>81000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>185600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>249100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>195400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>65600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>145800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>222900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>190000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>66500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>171200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>224700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>188200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>66700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>149200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>193500</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1134,8 +1147,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1249,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1336,64 +1353,67 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>6500</v>
+        <v>23500</v>
       </c>
       <c r="E14" s="3">
-        <v>52700</v>
+        <v>2800</v>
       </c>
       <c r="F14" s="3">
-        <v>-7700</v>
+        <v>50900</v>
       </c>
       <c r="G14" s="3">
-        <v>17400</v>
+        <v>-172400</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>15700</v>
       </c>
       <c r="I14" s="3">
-        <v>500</v>
+        <v>-3200</v>
       </c>
       <c r="J14" s="3">
+        <v>100</v>
+      </c>
+      <c r="K14" s="3">
         <v>3700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-156100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-14200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-4700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-15700</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>4500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
-      </c>
-      <c r="U14" s="3">
-        <v>800</v>
       </c>
       <c r="V14" s="3">
         <v>800</v>
@@ -1402,144 +1422,150 @@
         <v>800</v>
       </c>
       <c r="X14" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y14" s="3">
         <v>400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>14900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5900</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>2600</v>
       </c>
       <c r="AF14" s="3">
         <v>2600</v>
       </c>
       <c r="AG14" s="3">
-        <v>1500</v>
+        <v>2600</v>
       </c>
       <c r="AH14" s="3">
         <v>1500</v>
       </c>
       <c r="AI14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E15" s="3">
         <v>104400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>96000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>54400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>57500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>54800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>50900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>50000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>52100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>47200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>51200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>55700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>59100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>58200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>56300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>57600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>58100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>53900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>51800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>53000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>55100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>53600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>55400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>54200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>54000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>49700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>47000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>45800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>49000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>45000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>39700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>40100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1572,210 +1598,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>941600</v>
+        <v>966400</v>
       </c>
       <c r="E17" s="3">
-        <v>840300</v>
+        <v>938300</v>
       </c>
       <c r="F17" s="3">
-        <v>576700</v>
+        <v>788500</v>
       </c>
       <c r="G17" s="3">
-        <v>666800</v>
+        <v>586900</v>
       </c>
       <c r="H17" s="3">
-        <v>599500</v>
+        <v>651500</v>
       </c>
       <c r="I17" s="3">
-        <v>451400</v>
+        <v>601000</v>
       </c>
       <c r="J17" s="3">
+        <v>450900</v>
+      </c>
+      <c r="K17" s="3">
         <v>491000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>621600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>419300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>441000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>534800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>598400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>572200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>437200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>558400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>613100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>530900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>408900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>496600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>601200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>520500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>404900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>462500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>574400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>523800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>365900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>437300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>520300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>441600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>317300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>373700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>441200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>176700</v>
+        <v>204800</v>
       </c>
       <c r="E18" s="3">
-        <v>-35300</v>
+        <v>180000</v>
       </c>
       <c r="F18" s="3">
-        <v>83400</v>
+        <v>16500</v>
       </c>
       <c r="G18" s="3">
-        <v>128000</v>
+        <v>73300</v>
       </c>
       <c r="H18" s="3">
-        <v>129700</v>
+        <v>143300</v>
       </c>
       <c r="I18" s="3">
-        <v>-16000</v>
+        <v>128100</v>
       </c>
       <c r="J18" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="K18" s="3">
         <v>61300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>131100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>267300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-20100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>61900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>118800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>95700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>66200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>96500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>100100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-41700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>59900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>130900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>80400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-72300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>28500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>120300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>77100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-51500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>52700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>113900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>82500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-33000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>49300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>88200</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1811,513 +1844,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>8000</v>
+        <v>-8400</v>
       </c>
       <c r="E20" s="3">
-        <v>8900</v>
+        <v>-7600</v>
       </c>
       <c r="F20" s="3">
-        <v>15700</v>
+        <v>-8000</v>
       </c>
       <c r="G20" s="3">
-        <v>156700</v>
+        <v>146500</v>
       </c>
       <c r="H20" s="3">
-        <v>5400</v>
+        <v>-157100</v>
       </c>
       <c r="I20" s="3">
-        <v>5700</v>
+        <v>-3800</v>
       </c>
       <c r="J20" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="K20" s="3">
         <v>4700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>13100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-12600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>26300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>221100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-499100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-15500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>285100</v>
+        <v>312300</v>
       </c>
       <c r="E21" s="3">
-        <v>79900</v>
+        <v>291900</v>
       </c>
       <c r="F21" s="3">
-        <v>157000</v>
+        <v>120400</v>
       </c>
       <c r="G21" s="3">
-        <v>342700</v>
+        <v>-18800</v>
       </c>
       <c r="H21" s="3">
-        <v>191800</v>
+        <v>357800</v>
       </c>
       <c r="I21" s="3">
-        <v>43700</v>
+        <v>186700</v>
       </c>
       <c r="J21" s="3">
+        <v>40700</v>
+      </c>
+      <c r="K21" s="3">
         <v>118400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>187100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>320000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>35400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>132400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>179400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>159700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>54600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>140300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>150200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>157100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>103200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>188800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>138000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-12400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>110700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>177900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>131000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>326200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-335300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>128900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>11000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>76300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>129500</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E22" s="3">
         <v>52800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>51900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>28000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>27400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>22000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>24100</v>
-      </c>
-      <c r="P22" s="3">
-        <v>24200</v>
       </c>
       <c r="Q22" s="3">
         <v>24200</v>
       </c>
       <c r="R22" s="3">
+        <v>24200</v>
+      </c>
+      <c r="S22" s="3">
         <v>25500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>24600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>25600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>27800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>28100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>28900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>29400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>30100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>29900</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>28900</v>
       </c>
       <c r="AB22" s="3">
         <v>28900</v>
       </c>
       <c r="AC22" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AD22" s="3">
         <v>28800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>28700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>28900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>26000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>25000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>25100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>138700</v>
+      </c>
+      <c r="E23" s="3">
         <v>131900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-78300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>68300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>256600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>107200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-37700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>41800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>112500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>246700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-39500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>55300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>95900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>76200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-28700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>49500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>73200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>76100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-69600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>19200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>103800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>54700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-99500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>24900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>94800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>49100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-72700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>245100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-414000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>55500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-57300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>8700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>62400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E24" s="3">
         <v>25800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-11100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>64900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>23900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-6500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>24800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>53900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>20500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>18400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-19600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>17200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-22900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-17200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>45600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>25900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>20800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-16700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>415300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-498300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2417,210 +2466,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E26" s="3">
         <v>106100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-67300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>232700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>84700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>87700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>192800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-34800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>44400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>75400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>57800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>36300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>92800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>58900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-46700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>36400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>58200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>38000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-71500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>74000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>36900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-55900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-170200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>84300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>52100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-55100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>61100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E27" s="3">
         <v>106100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-66900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>230000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>83600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-30800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>86500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>190100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>43800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>74200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>56700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-22500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>90700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>57100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-45000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>35700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>55800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>36400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-68800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>71300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>35500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-53700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-171700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>81300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>50000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-52400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2720,8 +2778,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2773,8 +2834,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2791,11 +2852,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-17600</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2803,11 +2864,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>216900</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2815,14 +2876,17 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2922,8 +2986,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3023,210 +3090,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-8000</v>
+        <v>8400</v>
       </c>
       <c r="E32" s="3">
-        <v>-8900</v>
+        <v>7600</v>
       </c>
       <c r="F32" s="3">
-        <v>-15700</v>
+        <v>8000</v>
       </c>
       <c r="G32" s="3">
-        <v>-156700</v>
+        <v>-146500</v>
       </c>
       <c r="H32" s="3">
-        <v>-5400</v>
+        <v>157100</v>
       </c>
       <c r="I32" s="3">
-        <v>-5700</v>
+        <v>3800</v>
       </c>
       <c r="J32" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-13100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>12600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-26300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-221100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>499100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>15500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E33" s="3">
         <v>106100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-66900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>230000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>83600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-30800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>86500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>190100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>43800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>74200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>56700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-22500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>90700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>57100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-45000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>35700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>55800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>36400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-68800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-19200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>71300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>35500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-53700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>45200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>81300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>50000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-52400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3326,215 +3402,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E35" s="3">
         <v>106100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-66900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>230000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>83600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-30800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>86500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>190100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>43800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>74200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>56700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-22500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>90700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>57100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-45000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>35700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>55800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>36400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-68800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-19200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>71300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>35500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-53700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>45200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>81300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>50000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-52400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44562</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44198</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43827</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43463</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43099</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3570,8 +3655,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3607,109 +3693,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>737500</v>
+      </c>
+      <c r="E41" s="3">
         <v>538700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>498100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>374200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>197500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>230000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>379500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>520500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>471700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>465300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>287400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>381000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>258100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>469100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>359700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>418200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>288800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>253400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>199100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>311300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>182600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>67700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>64800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>128500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>64900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>50400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>178300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>383600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>287100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>353100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>156100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>143400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3809,435 +3899,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>606200</v>
+      </c>
+      <c r="E43" s="3">
         <v>584000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>466300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>297500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>416900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>405800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>251000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>263200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>397500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>365100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>252600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>294800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>367500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>345300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>267200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>263400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>353400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>324500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>242500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>266300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>386800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>340000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>212500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>233100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>301700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>268800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>180100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>198300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>295500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>247500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>154800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>162400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>247200</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>345200</v>
+      </c>
+      <c r="E44" s="3">
         <v>349100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>338500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>241400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>243100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>246300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>234600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>212500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>202800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>209900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>187000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>180800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>195300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>198200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>210900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>200300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>209800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>231900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>231400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>204800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>197000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>208100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>214000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>213900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>277400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>289700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>239400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>194000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>221100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>212100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>201900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>165100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>203900</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E45" s="3">
         <v>28900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>42000</v>
       </c>
-      <c r="F45" s="3">
-        <v>819100</v>
-      </c>
       <c r="G45" s="3">
+        <v>19100</v>
+      </c>
+      <c r="H45" s="3">
         <v>19700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>24200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>50900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>20600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>13800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>19200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>16100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>15700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>12400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>13700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>11700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>12400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>12000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>12800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1715400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1500800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1345000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1732100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>877200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>906300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>890900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1018400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1093300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1056500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>777800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>869600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>834800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1027900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>858400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>893300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>865500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>822000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>688300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>796300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>778400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>628400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>510600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>591500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>659700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>621300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>611600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>783600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>815300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>825100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>524900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>483700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>491100</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4314,210 +4419,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4376500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4443400</v>
       </c>
-      <c r="E48" s="3">
-        <v>4525600</v>
-      </c>
       <c r="F48" s="3">
+        <v>4506600</v>
+      </c>
+      <c r="G48" s="3">
         <v>2013400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2012900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2016000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1904100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1851600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1799500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1817300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1795400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1873100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1868500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1894000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1925900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1878700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1791600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1782600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1799200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1780200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1795400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1822800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1834300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1780100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1751800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1733700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1672900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1615400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1620100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1555800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1528300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1446500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1456500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2226800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2261300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2170100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1292900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1310300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1298200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1230000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1203900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1199000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1212700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1213300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1233100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1245200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1247800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1272900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1249100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1341000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1235600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1218400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1223200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1222900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1215800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1213300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1210500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1166500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1131300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1126100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1053200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1029800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>935900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>865700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>800200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>785700</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4617,8 +4731,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4718,8 +4835,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4727,100 +4847,103 @@
         <v>108500</v>
       </c>
       <c r="E52" s="3">
-        <v>89300</v>
+        <v>108500</v>
       </c>
       <c r="F52" s="3">
-        <v>111100</v>
+        <v>108300</v>
       </c>
       <c r="G52" s="3">
-        <v>164600</v>
+        <v>59100</v>
       </c>
       <c r="H52" s="3">
-        <v>175000</v>
+        <v>51200</v>
       </c>
       <c r="I52" s="3">
-        <v>190000</v>
+        <v>48200</v>
       </c>
       <c r="J52" s="3">
+        <v>45500</v>
+      </c>
+      <c r="K52" s="3">
         <v>181800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>193200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>204400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>356800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>263300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>268200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>282700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>294000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>286900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>294000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>271000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>286400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>267900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>245400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>287900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>303100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>275500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>318400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>338000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>346100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>335200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>527600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>48400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>53000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>51100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>47800</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4920,109 +5043,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8427200</v>
+      </c>
+      <c r="E54" s="3">
         <v>8314000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8129900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5149600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4365000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4395500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4214900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4255700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4285000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4290800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4143200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4239100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4216600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4452400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4351300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4308000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4292200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4111200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3992300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4067600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4042100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3954900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3861400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3857600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3896300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3824300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3756600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3787300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3992800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3365200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2971900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2781500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2781000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5058,8 +5187,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5095,614 +5225,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E57" s="3">
         <v>282100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>290900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>123600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>173100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>171200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>139000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>104000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>166600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>167600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>146300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>128200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>155900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>152300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>150200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>120800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>149500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>138300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>122400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>116400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>152200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>131400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>101800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>107700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>140200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>144300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>110300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>98700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>134900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>116800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>105400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>81600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>113300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>12600</v>
+        <v>32100</v>
       </c>
       <c r="E58" s="3">
-        <v>12300</v>
+        <v>29800</v>
       </c>
       <c r="F58" s="3">
-        <v>7800</v>
+        <v>29000</v>
       </c>
       <c r="G58" s="3">
-        <v>7200</v>
+        <v>16400</v>
       </c>
       <c r="H58" s="3">
-        <v>8600</v>
+        <v>16000</v>
       </c>
       <c r="I58" s="3">
-        <v>9300</v>
+        <v>16300</v>
       </c>
       <c r="J58" s="3">
+        <v>16800</v>
+      </c>
+      <c r="K58" s="3">
         <v>12100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>24000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>23800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>25700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>27600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>31000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>32800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>31200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>28700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>23900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>23600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>22600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>22200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>21900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>19700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>23800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>29100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>24000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>27000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>26300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>23900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>18300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>279100</v>
+        <v>109700</v>
       </c>
       <c r="E59" s="3">
-        <v>218800</v>
+        <v>53900</v>
       </c>
       <c r="F59" s="3">
-        <v>191500</v>
+        <v>51500</v>
       </c>
       <c r="G59" s="3">
-        <v>168500</v>
+        <v>26200</v>
       </c>
       <c r="H59" s="3">
+        <v>35800</v>
+      </c>
+      <c r="I59" s="3">
+        <v>39000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>31600</v>
+      </c>
+      <c r="K59" s="3">
+        <v>139800</v>
+      </c>
+      <c r="L59" s="3">
+        <v>140100</v>
+      </c>
+      <c r="M59" s="3">
+        <v>148000</v>
+      </c>
+      <c r="N59" s="3">
+        <v>138200</v>
+      </c>
+      <c r="O59" s="3">
+        <v>156900</v>
+      </c>
+      <c r="P59" s="3">
+        <v>151200</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>163900</v>
+      </c>
+      <c r="R59" s="3">
+        <v>143800</v>
+      </c>
+      <c r="S59" s="3">
+        <v>170900</v>
+      </c>
+      <c r="T59" s="3">
+        <v>173600</v>
+      </c>
+      <c r="U59" s="3">
         <v>167200</v>
       </c>
-      <c r="I59" s="3">
-        <v>112200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>139800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>140100</v>
-      </c>
-      <c r="L59" s="3">
-        <v>148000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>138200</v>
-      </c>
-      <c r="N59" s="3">
-        <v>156900</v>
-      </c>
-      <c r="O59" s="3">
-        <v>151200</v>
-      </c>
-      <c r="P59" s="3">
-        <v>163900</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>143800</v>
-      </c>
-      <c r="R59" s="3">
-        <v>170900</v>
-      </c>
-      <c r="S59" s="3">
-        <v>173600</v>
-      </c>
-      <c r="T59" s="3">
-        <v>167200</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>134800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>159000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>156200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>150900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>135200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>131000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>126500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>131400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>141800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>127200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>153200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>134000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>114000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>139500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>134700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>552800</v>
+      </c>
+      <c r="E60" s="3">
         <v>573900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>522000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>323000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>348900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>347000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>260500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>255800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>322800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>333000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>305100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>309100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>330900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>341900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>321700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>322700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>355900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>336700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>285800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>299300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>332100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>304800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>259300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>260700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>286400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>299500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>281300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>250000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>315100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>277200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>243300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>239300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>267300</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2804500</v>
+        <v>2884200</v>
       </c>
       <c r="E61" s="3">
-        <v>2804900</v>
+        <v>2881900</v>
       </c>
       <c r="F61" s="3">
-        <v>2298000</v>
+        <v>2883500</v>
       </c>
       <c r="G61" s="3">
-        <v>1493200</v>
+        <v>2331200</v>
       </c>
       <c r="H61" s="3">
-        <v>1493100</v>
+        <v>1528100</v>
       </c>
       <c r="I61" s="3">
-        <v>1494100</v>
+        <v>1526700</v>
       </c>
       <c r="J61" s="3">
+        <v>1528400</v>
+      </c>
+      <c r="K61" s="3">
         <v>1495700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1606000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1728300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2031700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2035900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1924100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1893200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1849500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1850300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1851100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1853400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1854200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1855300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1807500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1808200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1807300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1808500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1810800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1807100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1807700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1513100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1514500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1515400</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>602800</v>
+        <v>337400</v>
       </c>
       <c r="E62" s="3">
-        <v>584400</v>
+        <v>336400</v>
       </c>
       <c r="F62" s="3">
-        <v>212000</v>
+        <v>300100</v>
       </c>
       <c r="G62" s="3">
-        <v>215100</v>
+        <v>163000</v>
       </c>
       <c r="H62" s="3">
-        <v>481400</v>
+        <v>180300</v>
       </c>
       <c r="I62" s="3">
-        <v>480400</v>
+        <v>447900</v>
       </c>
       <c r="J62" s="3">
+        <v>446100</v>
+      </c>
+      <c r="K62" s="3">
         <v>492100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1982700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2007900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2081100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>500800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>385700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>383900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>379100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>445000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>473600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>463100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>460300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>472400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>469900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>473100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>468300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>447300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>442900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>439700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>431400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>454800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>653200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>167300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>167800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>167700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5802,8 +5951,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5903,8 +6055,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6004,109 +6159,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3980600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3981200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3911300</v>
       </c>
-      <c r="F66" s="3">
-        <v>2842500</v>
-      </c>
       <c r="G66" s="3">
-        <v>2071400</v>
+        <v>2833000</v>
       </c>
       <c r="H66" s="3">
-        <v>2334900</v>
+        <v>2057200</v>
       </c>
       <c r="I66" s="3">
-        <v>2247200</v>
+        <v>2321500</v>
       </c>
       <c r="J66" s="3">
+        <v>2235000</v>
+      </c>
+      <c r="K66" s="3">
         <v>2256400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2326300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2361800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2406000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2425600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2454800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2768000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2749700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2710200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2740900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2665500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2610700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2640100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2670700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2645300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2594500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2529900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2551500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2557800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2531600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2528800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2791200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2265600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1937200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1939400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2006400</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6142,8 +6303,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6243,8 +6405,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6344,8 +6509,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6445,8 +6613,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6546,109 +6717,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1021100</v>
+      </c>
+      <c r="E72" s="3">
         <v>916000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>809900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>876800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>873800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>643700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>560100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>590900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>620300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>587300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>397200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>479000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>435100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>360900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>304300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>326800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>291600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>200900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>143800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>188800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>153100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>97400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>61000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>129700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>148900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>77600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>42100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>95800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>95600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-33400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>19000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6748,8 +6925,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6849,8 +7029,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6950,109 +7133,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4446600</v>
+      </c>
+      <c r="E76" s="3">
         <v>4332700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4218600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2307000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2293600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2060600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1967700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1999300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1958600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1929000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1737300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1813600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1761900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1684400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1601500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1597800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1551200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1445700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1381600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1427400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1371400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1309500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1266900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1327700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1344900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1266400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1224900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1258500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1201600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1099500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1034600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>842000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>774600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7152,215 +7341,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44562</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44198</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43827</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43463</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43099</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E81" s="3">
         <v>106100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-66900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>230000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>83600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-30800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>86500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>190100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>43800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>74200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>56700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-22500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>90700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>57100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-45000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>35700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>55800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>36400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-68800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-19200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>71300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>35500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-53700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>45200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>81300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>50000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-52400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7396,109 +7594,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100300</v>
+        <v>56500</v>
       </c>
       <c r="E83" s="3">
-        <v>106400</v>
+        <v>55100</v>
       </c>
       <c r="F83" s="3">
-        <v>57900</v>
+        <v>52300</v>
       </c>
       <c r="G83" s="3">
-        <v>58100</v>
+        <v>50900</v>
       </c>
       <c r="H83" s="3">
-        <v>56700</v>
+        <v>51200</v>
       </c>
       <c r="I83" s="3">
-        <v>53900</v>
+        <v>51100</v>
       </c>
       <c r="J83" s="3">
+        <v>53200</v>
+      </c>
+      <c r="K83" s="3">
         <v>52300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>52700</v>
       </c>
       <c r="L83" s="3">
         <v>52700</v>
       </c>
       <c r="M83" s="3">
+        <v>52700</v>
+      </c>
+      <c r="N83" s="3">
         <v>54800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>57400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>59400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>59300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>59100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>65300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>52400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>55400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>54700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>55900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>56000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>53900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>57000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>55900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>54300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>53000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>45600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>52500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>49900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>47400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>43300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>42600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7598,8 +7800,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7699,8 +7904,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7800,8 +8008,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7901,8 +8112,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8002,109 +8216,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>232800</v>
+      </c>
+      <c r="E89" s="3">
         <v>151600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-40200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>195200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>149600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>93700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>151900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>115900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>33000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-16700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>154600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>132700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>96000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>190800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>156300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>100600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-38900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>173300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>147900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>46600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-30700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>138800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>104300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>17600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-51400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>159800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>121300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>56700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-45500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>160300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8140,109 +8360,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-99200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-117400</v>
       </c>
-      <c r="E91" s="3">
-        <v>-79900</v>
-      </c>
       <c r="F91" s="3">
+        <v>-58500</v>
+      </c>
+      <c r="G91" s="3">
         <v>-73400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-55300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-63300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-63600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-77700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-71800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-57800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-37300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-63000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-69800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-37200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-34300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-43900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-61800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-37700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-34200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-43400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-62200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-36900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-52100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-82200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-46700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-51100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-31500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8342,8 +8566,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8443,109 +8670,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-109000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1103400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-54900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-242300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-118300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-93100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>223900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-25900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>4900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-34500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-32600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-155500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-40600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-56900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-33000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-28900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-38400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-62400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-67700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-81900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-115800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-154200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-47000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-191800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-155600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-158100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-35000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-58300</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8581,31 +8814,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8682,8 +8916,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8783,8 +9020,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8884,8 +9124,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8985,307 +9228,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>468700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>785000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-126600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-23100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-10300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-82700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-78300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-67700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-307600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-29300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>34300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-15600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-11700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>29200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-29600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-16300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>4000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>295800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>216200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-13400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-30100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="E101" s="3">
-        <v>-1100</v>
+        <v>700</v>
       </c>
       <c r="F101" s="3">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="G101" s="3">
+        <v>300</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
-        <v>700</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
+        <v>200</v>
+      </c>
+      <c r="K101" s="3">
+        <v>300</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="N101" s="3">
+        <v>200</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
-        <v>300</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="S101" s="3">
+        <v>600</v>
+      </c>
+      <c r="T101" s="3">
+        <v>200</v>
+      </c>
+      <c r="U101" s="3">
+        <v>400</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="W101" s="3">
+        <v>100</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>100</v>
-      </c>
-      <c r="R101" s="3">
-        <v>600</v>
-      </c>
-      <c r="S101" s="3">
-        <v>200</v>
-      </c>
-      <c r="T101" s="3">
-        <v>400</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="V101" s="3">
-        <v>100</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>500</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>100</v>
       </c>
       <c r="AG101" s="3">
         <v>100</v>
       </c>
       <c r="AH101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>198800</v>
+      </c>
+      <c r="E102" s="3">
         <v>40600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-676100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>976700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-32500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-149400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-141000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>48800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>177900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-93600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>122900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-211000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>109400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-58400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>129400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>35400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>54300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-112200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>128700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>114900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-63700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>63600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>14500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-127900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-205300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>96500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-66000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>197000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>12700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>111700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>22500</v>
       </c>
     </row>
